--- a/incident_report_forms/011_incident_response_monitoring_form--incident_report_forms.xlsx
+++ b/incident_report_forms/011_incident_response_monitoring_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'north_america'}</t>
+          <t>north_america</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'North America'}</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'south_america'}</t>
+          <t>south_america</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'South America'}</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'server'}</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Server'}</t>
+          <t>Server</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'system'}</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'System'}</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'success'}</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Success'}</t>
+          <t>Success</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'failure'}</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Failure'}</t>
+          <t>Failure</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'report_1'}</t>
+          <t>report_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Report 1'}</t>
+          <t>Report 1</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'report_2'}</t>
+          <t>report_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Report 2'}</t>
+          <t>Report 2</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'report_3'}</t>
+          <t>report_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Report 3'}</t>
+          <t>Report 3</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'chatjimmy1'}</t>
+          <t>chatjimmy1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'chatjimmy1'}</t>
+          <t>chatjimmy1</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
     </row>
